--- a/ExcelDynamicCase/publish/ExcelDynamicCase.xlsx
+++ b/ExcelDynamicCase/publish/ExcelDynamicCase.xlsx
@@ -829,7 +829,7 @@
 </file>
 
 <file path=vstoDataStore/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{86B6D9CD-6BBA-478B-A1EA-41DA8861598A}">
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{64540429-58EF-4213-B9B7-535031887D88}">
   <ds:schemaRefs/>
 </ds:datastoreItem>
 </file>